--- a/Annotation_Main/Main1/Main1_consolidation.xlsx
+++ b/Annotation_Main/Main1/Main1_consolidation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katja/Dropbox/Doktorat/ParlaMint/Sentiment_annotation/Sentiment_aggregation/Annotation_Main/Main1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katja/Dropbox/Doktorat/ParlaMint/Sentiment_annotation-speeches/Annotation_Main/Main1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED318EC4-59B7-A046-ADBF-517DB816244B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C81D31-B9F5-E344-9512-B4BF316B20A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" xr2:uid="{55C80BA5-D1F4-9D49-8F6B-B8589FADD4B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Main1_consolidation" localSheetId="0">Sheet1!$A$1:$J$199</definedName>
+    <definedName name="Main1_consolidation" localSheetId="0">Sheet1!$A$1:$L$201</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="590">
   <si>
     <t>ID</t>
   </si>
@@ -1792,16 +1792,61 @@
   </si>
   <si>
     <t xml:space="preserve">The speaker is procedure leader, but also with a flare. </t>
+  </si>
+  <si>
+    <t>sent_tamara</t>
+  </si>
+  <si>
+    <t>sent_katja</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>ParlaMint-SI_2013-12-17-SDZ6-Redna-20.u188</t>
+  </si>
+  <si>
+    <t>Hvala lepa. Upam, da bo šlo brez prekinjanja. Zahteval sem razpravo o odgovoru ministra za pravosodje. Šlo je za vprašanje nezakonitega imenovanja direktorja Vrhovnega državnega tožilstva, ki ga je izvedel v sodelovanju s Sodnim svetom generalni državni tožilec gospod Fišer. Šlo je za to, da je bilo to imenovanje opravljeno 1 dan pred imenovanjem zadnje Janševe vlade. Pri tem sem takrat kot minister smatral, da gre za nezakonito imenovanje, zato smo na vladi to imenovanje odpravili. Gospod Škrlec se je pritožil na Upravno sodišče in – pazite! – Upravno sodišče je ugotovilo, da je generalni državni tožilec zlorabil zakon, ponavljam, generalni državni tožilec je zlorabil zakon. Zato sem takrat v vlogi ministra, pristojnega tudi za tožilstvo, sprejel sklep o tem, da opravimo nadzor v tej zadevi. Generalni državni tožilec je bil poln besed v medijih, kako politično pritiskam na njega, in je ta nadzor odklonil, kar ima po zakonu pravico. Zato je vlada 13. marca letošnjega leta sprejela sklep, da se ta nadzor vseeno opravi. Sedanja vlada pa je pred približno 10 dnevi to odločitev odpravila. To pomeni, da nadzora nad delom generalnega državnega tožilca niti v tej zadevi niti v kakšni drugi zadevi ne bo. Minister je včeraj sicer govoril o tem, da bo pripravil nadzor nad delom generalnega državnega tožilca, vendar bomo videli, ali bo ali ne bo. Naj vas spomnim tudi na neko drugo stvar, ki je pomembna pri glasovanju o tem proceduralnem predlogu za razpravo. Vse več je podatkov, da je Vrhovno državno tožilstvo z gospodom Fišerjem na čelu, če bi rekel v jeziku prejšnjega sistema, neka zlonamerna celica v tej državi, ki pripravlja nekatere stvari, ki nimajo zakonite podlage; posebej poudarjam – ki nimajo zakonite podlage. Prvič, dobro se spomnite pisanja medijev o tem, kako naj bi med imenovanjem, ko smo glasovali o gospodu Jankoviću kot premierju, in potem med drugim glasovanjem uporabil tožilske podatke in preko bivšega predsednika države gospoda Kučana in gospoda Türka vplival na tiste odločitve. Spomnite se tudi drugega primera [[...]] [[opozorilni znak za konec razprave]] Bom prosil še za obrazložitev glasu v svojem imenu. Hvala.</t>
+  </si>
+  <si>
+    <t>Clear disdain</t>
+  </si>
+  <si>
+    <t>ParlaMint-SI_2005-04-20-SDZ4-Redna-05.u156</t>
+  </si>
+  <si>
+    <t>Hvala za besedo, gospod podpredsednik. Lep pozdrav gospodu ministru, kolegicam in kolegom! Sam bom z veseljem podprl gospo Barbaro Brezigar. Iz današnje razprave sem pač zaznal, da ji je bilo očitanih več stvari, ena od teh je politična opredeljenost, vendar bi tudi njeni predhodnici ne mogli ničesar drugega reči, saj je bila tudi zaznavno politično opredeljena. Nadalje, imamo celo ustavnega sodnika, ki izvira še iz tiste generacije, ki je izšla v solzah iz Beograda. Pa me to nič ne moti, če bi delo opravljali strokovno in če bi bila v Sloveniji zagotovljena pravna varnost. Glede strokovnih referenc mislim, da jih ima kandidatka zadosti in da tu ni nobenega vprašanja. Potem je bilo omenjeno, da je bila na razpisu edina kandidatka. Tudi včasih so bili razpisi, kjer je bil znan kandidat, plus dva ali trije zaradi fasade ali zaradi lepšega. Sam predvsem pričakujem, da se bo stanje stabiliziralo in bodo moje slabe izkušnje iz preteklosti oziroma strahovi odpravljeni. V mislih imam predvsem primere, ko je v Ljubljani prišlo večkrat do streljanja, Ljubljana je bila že podobna malemu Divjemu zahodu, in če se je zadeva lahko opredelila kot svinjarija, je ni bilo treba kazensko preganjati, kajti vsaka svinjarija še ni [[...]]in tako naprej. No, tudi v Lescah je prišlo že pred leti do tega, da sta se dva skregala zaradi parkirnega mesta, človek je potegnil pištolo in drugega ustrelil. Zaradi zelo učinkovitega sodnega pregona je morilec še danes na varnem v Črni gori. Glavni finančni mahinator je tudi pobegnil roki pravice in ga je pravica ujela šele v Združenih državah Amerike. Upam, da do njegove izročitve še dolgo časa ne bo prišlo, kajti v vmesnem času je v zaporu v ZDA in bo vsaj tam odsedel tisti svoj del. Nadalje, na visokih položajih v sodstvu so zaposlovali svoje življenjske sopotnike, sopotnice, z neustrezno izobrazbo, vendar s plačo, kot da bi to izobrazbo imeli. Najbolj vzorčen primer je pa morda umor v Tekačevem, kjer je osumljeni očitno z zadevami nadaljeval še naprej in so ga v prekršku našli šele v drugi državi, kjer so pa pokazali, kaj je učinkovitost - takoj je bil na vrsti za sojenje in takoj zaprt. Takih primerov je bilo še več, in upam, da se bodo z nastopom nove generalne tožilke te moje slabe izkušnje iz preteklosti, ti strahovi, da bodo odpravljeni. Hvala lepa.</t>
+  </si>
+  <si>
+    <t>Partially talks about bad experiences, but expresses general support.</t>
+  </si>
+  <si>
+    <t>This one is ..wow. It goes from expressed support to one of the  MPs(?), into a monolouge of vey problematic cases of applying to positions, and then directly to shootings, to illustrate why he supports her and his hopes for positive change she could bring. But majority of the speech is negative, so this could also be Negative</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1851,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1872,6 +1917,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2190,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA21A747-F629-654D-AD9A-57790E7F3BD2}">
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" bestFit="1" customWidth="1"/>
@@ -2200,11 +2248,12 @@
     <col min="6" max="6" width="28" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" customWidth="1"/>
     <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="9" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.83203125" style="11"/>
+    <col min="11" max="11" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2229,14 +2278,20 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2255,14 +2310,20 @@
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="I2" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2278,14 +2339,20 @@
       <c r="E3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="323" x14ac:dyDescent="0.2">
+      <c r="I3" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2304,14 +2371,20 @@
       <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -2333,14 +2406,20 @@
       <c r="H5" t="s">
         <v>29</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2356,14 +2435,20 @@
       <c r="E6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I6" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2379,14 +2464,20 @@
       <c r="E7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="289" x14ac:dyDescent="0.2">
+      <c r="I7" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -2402,14 +2493,20 @@
       <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -2425,14 +2522,20 @@
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I9" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -2448,14 +2551,20 @@
       <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I10" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -2471,14 +2580,20 @@
       <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="I11" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -2500,14 +2615,20 @@
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I12" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2523,14 +2644,20 @@
       <c r="E13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I13" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -2546,14 +2673,20 @@
       <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I14" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -2572,14 +2705,20 @@
       <c r="F15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -2595,14 +2734,20 @@
       <c r="E16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I16" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -2618,14 +2763,20 @@
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I17" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2644,14 +2795,20 @@
       <c r="H18" t="s">
         <v>29</v>
       </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="I18" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -2667,14 +2824,20 @@
       <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="340" x14ac:dyDescent="0.2">
+      <c r="I19" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="340" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2696,14 +2859,20 @@
       <c r="H20" t="s">
         <v>29</v>
       </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="I20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -2725,14 +2894,20 @@
       <c r="H21" t="s">
         <v>29</v>
       </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -2748,14 +2923,20 @@
       <c r="E22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I22" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>77</v>
       </c>
@@ -2771,14 +2952,20 @@
       <c r="E23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I23" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -2794,14 +2981,20 @@
       <c r="E24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I24" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -2823,14 +3016,20 @@
       <c r="G25" t="s">
         <v>29</v>
       </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="I25" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="238" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -2852,14 +3051,20 @@
       <c r="G26" t="s">
         <v>29</v>
       </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I26" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -2881,14 +3086,20 @@
       <c r="G27" t="s">
         <v>29</v>
       </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>93</v>
       </c>
@@ -2904,14 +3115,20 @@
       <c r="E28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="356" x14ac:dyDescent="0.2">
+      <c r="I28" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="356" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -2927,14 +3144,20 @@
       <c r="E29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="I29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -2956,14 +3179,20 @@
       <c r="G30" t="s">
         <v>29</v>
       </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="I30" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -2979,14 +3208,20 @@
       <c r="E31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -3002,14 +3237,20 @@
       <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I32" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -3031,14 +3272,20 @@
       <c r="H33" t="s">
         <v>29</v>
       </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
+      <c r="I33" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -3054,14 +3301,20 @@
       <c r="E34" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I34" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="I34" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="255" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>114</v>
       </c>
@@ -3083,14 +3336,20 @@
       <c r="G35" t="s">
         <v>29</v>
       </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="I35" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>118</v>
       </c>
@@ -3112,14 +3371,20 @@
       <c r="H36" t="s">
         <v>29</v>
       </c>
-      <c r="I36" t="b">
-        <v>1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="I36" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="3" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>121</v>
       </c>
@@ -3136,14 +3401,20 @@
         <v>124</v>
       </c>
       <c r="F37" s="2"/>
-      <c r="I37" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="s">
+      <c r="I37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>125</v>
       </c>
@@ -3159,14 +3430,20 @@
       <c r="E38" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="I38" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>128</v>
       </c>
@@ -3182,14 +3459,20 @@
       <c r="E39" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I39" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I39" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>130</v>
       </c>
@@ -3205,14 +3488,20 @@
       <c r="E40" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="372" x14ac:dyDescent="0.2">
+      <c r="I40" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="372" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -3231,14 +3520,20 @@
       <c r="F41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" s="3" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="I41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="3" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>136</v>
       </c>
@@ -3260,14 +3555,20 @@
       <c r="H42" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="s">
+      <c r="I42" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>139</v>
       </c>
@@ -3283,14 +3584,20 @@
       <c r="E43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I43" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>141</v>
       </c>
@@ -3306,14 +3613,20 @@
       <c r="E44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I44" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>143</v>
       </c>
@@ -3329,14 +3642,20 @@
       <c r="E45" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I45" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -3352,14 +3671,20 @@
       <c r="E46" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I46" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>147</v>
       </c>
@@ -3375,14 +3700,20 @@
       <c r="E47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I47" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -3398,14 +3729,20 @@
       <c r="E48" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I48" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>151</v>
       </c>
@@ -3421,14 +3758,20 @@
       <c r="E49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I49" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>153</v>
       </c>
@@ -3444,42 +3787,61 @@
       <c r="E50" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="I50" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="H51" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C51" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>158</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="C52" t="s">
         <v>17</v>
@@ -3490,19 +3852,25 @@
       <c r="E52" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I52" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C53" t="s">
         <v>17</v>
@@ -3513,414 +3881,516 @@
       <c r="E53" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="I53" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>160</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>162</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C54" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="C55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="I55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>165</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C55" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="I56" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C56" t="s">
-        <v>26</v>
-      </c>
-      <c r="D56" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="I57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>171</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C57" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="I58" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>68</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>68</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H59" t="s">
         <v>29</v>
       </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="I59" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="60" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>177</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C59" t="s">
-        <v>21</v>
-      </c>
-      <c r="D59" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="I60" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>180</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C60" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" t="s">
-        <v>17</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H61" t="s">
         <v>29</v>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="I61" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C61" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="170" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="I62" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
         <v>187</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C62" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="C63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" t="s">
         <v>68</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H63" t="s">
         <v>29</v>
       </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" t="s">
+      <c r="I63" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="187" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="64" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C63" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" t="s">
-        <v>26</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="C64" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I63" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="170" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="I64" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>193</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="I65" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>196</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C65" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="I66" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
         <v>198</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C66" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H67" t="s">
         <v>29</v>
       </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="I67" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="68" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>202</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" s="4" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
+      <c r="I68" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="4" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B69" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C69" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" s="5" t="s">
+      <c r="D69" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="F69" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I68" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="I69" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>208</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>210</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
@@ -3931,68 +4401,86 @@
       <c r="E70" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
+      <c r="I70" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>210</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A72" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B72" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71" s="7" t="s">
+      <c r="C72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F72" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="I71" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="I72" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K72" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>216</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>218</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
@@ -4003,19 +4491,25 @@
       <c r="E73" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I73" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
@@ -4026,570 +4520,708 @@
       <c r="E74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="I74" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>222</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C75" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" t="s">
-        <v>21</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="289" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="I76" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="289" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>225</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C76" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="C77" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="I77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>228</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C77" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="C78" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="238" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="I78" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>231</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C80" t="s">
         <v>123</v>
-      </c>
-      <c r="D78" t="s">
-        <v>123</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="404" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>235</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C79" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>238</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C80" t="s">
-        <v>68</v>
       </c>
       <c r="D80" t="s">
         <v>123</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J80" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>235</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>238</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>123</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="s">
+      <c r="I82" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+    <row r="83" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>242</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C81" t="s">
-        <v>17</v>
-      </c>
-      <c r="D81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="C83" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I81" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="I83" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J83" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>244</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C82" t="s">
-        <v>17</v>
-      </c>
-      <c r="D82" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="C84" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="272" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="I84" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J84" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>248</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C83" t="s">
-        <v>17</v>
-      </c>
-      <c r="D83" t="s">
-        <v>68</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="H83" t="s">
-        <v>29</v>
-      </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>252</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C84" t="s">
-        <v>26</v>
-      </c>
-      <c r="D84" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="272" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>256</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D85" t="s">
         <v>68</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H85" t="s">
         <v>29</v>
       </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="s">
+      <c r="I85" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>252</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C86" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I86" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="255" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="E87" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H87" t="s">
+        <v>29</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>260</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C86" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" t="s">
-        <v>26</v>
-      </c>
-      <c r="E86" s="1" t="s">
+      <c r="C88" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="187" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="I88" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>263</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C87" t="s">
-        <v>26</v>
-      </c>
-      <c r="D87" t="s">
-        <v>26</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="C89" t="s">
+        <v>26</v>
+      </c>
+      <c r="D89" t="s">
+        <v>26</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="I89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
         <v>266</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C90" t="s">
         <v>68</v>
       </c>
-      <c r="D88" t="s">
-        <v>21</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="D90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F90" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="I90" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>270</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C89" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="1" t="s">
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I89" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="I91" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J91" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K91" t="b">
+        <v>1</v>
+      </c>
+      <c r="L91" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>272</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C92" t="s">
         <v>123</v>
       </c>
-      <c r="D90" t="s">
-        <v>26</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="D92" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F92" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="I92" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J92" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>275</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C91" t="s">
-        <v>26</v>
-      </c>
-      <c r="D91" t="s">
-        <v>26</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="C93" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F93" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="I93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>278</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C92" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" t="s">
-        <v>17</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I92" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="I94" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J94" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K94" t="b">
+        <v>1</v>
+      </c>
+      <c r="L94" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
         <v>280</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C93" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="1" t="s">
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H95" t="s">
         <v>29</v>
       </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="I95" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>284</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C96" t="s">
         <v>123</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D96" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H96" t="s">
         <v>29</v>
       </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="s">
+      <c r="I96" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+    <row r="97" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
         <v>287</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B97" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="C95" t="s">
-        <v>17</v>
-      </c>
-      <c r="D95" t="s">
-        <v>17</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I95" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>289</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C96" t="s">
-        <v>17</v>
-      </c>
-      <c r="D96" t="s">
-        <v>17</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I96" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>291</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -4600,19 +5232,25 @@
       <c r="E97" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I97" t="b">
-        <v>1</v>
-      </c>
-      <c r="J97" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="I97" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K97" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
@@ -4623,19 +5261,25 @@
       <c r="E98" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I98" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I98" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J98" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K98" t="b">
+        <v>1</v>
+      </c>
+      <c r="L98" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
@@ -4646,42 +5290,54 @@
       <c r="E99" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I99" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I99" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L99" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C100" t="s">
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J100" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K100" t="b">
+        <v>1</v>
+      </c>
+      <c r="L100" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
@@ -4692,146 +5348,179 @@
       <c r="E101" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I101" t="b">
-        <v>1</v>
-      </c>
-      <c r="J101" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="I101" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K101" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>297</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
+        <v>26</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J102" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>300</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I103" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J103" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K103" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
         <v>302</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C102" t="s">
-        <v>17</v>
-      </c>
-      <c r="D102" t="s">
-        <v>17</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F104" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H104" t="s">
         <v>29</v>
       </c>
-      <c r="I102" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="I104" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
         <v>305</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C103" t="s">
-        <v>26</v>
-      </c>
-      <c r="D103" t="s">
-        <v>26</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="C105" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105" t="s">
+        <v>26</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="I103" t="b">
-        <v>0</v>
-      </c>
-      <c r="J103" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="272" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="I105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
         <v>309</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C104" t="s">
-        <v>21</v>
-      </c>
-      <c r="D104" t="s">
-        <v>21</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="C106" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="I104" t="b">
-        <v>0</v>
-      </c>
-      <c r="J104" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="I106" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
         <v>312</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="C105" t="s">
-        <v>17</v>
-      </c>
-      <c r="D105" t="s">
-        <v>17</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I105" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="187" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>314</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C106" t="s">
-        <v>17</v>
-      </c>
-      <c r="D106" t="s">
-        <v>26</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="I106" t="b">
-        <v>0</v>
-      </c>
-      <c r="J106" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>318</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="C107" t="s">
         <v>17</v>
@@ -4842,42 +5531,57 @@
       <c r="E107" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I107" t="b">
-        <v>1</v>
-      </c>
-      <c r="J107" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="I107" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K107" t="b">
+        <v>1</v>
+      </c>
+      <c r="L107" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C108" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D108" t="s">
         <v>26</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="I108" t="b">
-        <v>0</v>
-      </c>
-      <c r="J108" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="I108" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J108" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C109" t="s">
         <v>17</v>
@@ -4888,51 +5592,54 @@
       <c r="E109" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I109" t="b">
-        <v>1</v>
-      </c>
-      <c r="J109" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="323" x14ac:dyDescent="0.2">
+      <c r="I109" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J109" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K109" t="b">
+        <v>1</v>
+      </c>
+      <c r="L109" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C110" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D110" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G110" t="s">
-        <v>29</v>
-      </c>
-      <c r="H110" t="s">
-        <v>29</v>
-      </c>
-      <c r="I110" t="b">
-        <v>0</v>
-      </c>
-      <c r="J110" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+      <c r="I110" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J110" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C111" t="s">
         <v>17</v>
@@ -4943,140 +5650,179 @@
       <c r="E111" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I111" t="b">
-        <v>1</v>
-      </c>
-      <c r="J111" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="I111" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K111" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>325</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C112" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G112" t="s">
+        <v>29</v>
+      </c>
+      <c r="H112" t="s">
+        <v>29</v>
+      </c>
+      <c r="I112" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J112" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>329</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I113" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J113" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K113" t="b">
+        <v>1</v>
+      </c>
+      <c r="L113" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
         <v>331</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C112" t="s">
-        <v>26</v>
-      </c>
-      <c r="D112" t="s">
-        <v>26</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="C114" t="s">
+        <v>26</v>
+      </c>
+      <c r="D114" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I112" t="b">
-        <v>0</v>
-      </c>
-      <c r="J112" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="102" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+      <c r="I114" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J114" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
         <v>334</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C113" t="s">
-        <v>26</v>
-      </c>
-      <c r="D113" t="s">
-        <v>26</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="C115" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="I113" t="b">
-        <v>0</v>
-      </c>
-      <c r="J113" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="238" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+      <c r="I115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+      <c r="L115" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
         <v>337</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C114" t="s">
-        <v>26</v>
-      </c>
-      <c r="D114" t="s">
-        <v>26</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="C116" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="I114" t="b">
-        <v>0</v>
-      </c>
-      <c r="J114" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+      <c r="I116" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
         <v>340</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
-      </c>
-      <c r="D115" t="s">
-        <v>17</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I115" t="b">
-        <v>1</v>
-      </c>
-      <c r="J115" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="136" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>342</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C116" t="s">
-        <v>68</v>
-      </c>
-      <c r="D116" t="s">
-        <v>68</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="H116" t="s">
-        <v>29</v>
-      </c>
-      <c r="I116" t="b">
-        <v>0</v>
-      </c>
-      <c r="J116" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>346</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="C117" t="s">
         <v>17</v>
@@ -5087,120 +5833,150 @@
       <c r="E117" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I117" t="b">
-        <v>1</v>
-      </c>
-      <c r="J117" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I117" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J117" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K117" t="b">
+        <v>1</v>
+      </c>
+      <c r="L117" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>342</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>68</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H118" t="s">
+        <v>29</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+      <c r="L118" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>346</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J119" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K119" t="b">
+        <v>1</v>
+      </c>
+      <c r="L119" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
         <v>348</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C118" t="s">
-        <v>17</v>
-      </c>
-      <c r="D118" t="s">
-        <v>17</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="I118" t="b">
-        <v>0</v>
-      </c>
-      <c r="J118" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+      <c r="I120" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J120" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+      <c r="L120" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>351</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B121" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C119" t="s">
-        <v>21</v>
-      </c>
-      <c r="D119" t="s">
-        <v>21</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" t="s">
+        <v>21</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F121" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="I119" t="b">
-        <v>0</v>
-      </c>
-      <c r="J119" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+      <c r="I121" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+      <c r="L121" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
         <v>354</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B122" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="C120" t="s">
-        <v>17</v>
-      </c>
-      <c r="D120" t="s">
-        <v>17</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="H120" t="s">
-        <v>29</v>
-      </c>
-      <c r="I120" t="b">
-        <v>1</v>
-      </c>
-      <c r="J120" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="170" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>357</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C121" t="s">
-        <v>17</v>
-      </c>
-      <c r="D121" t="s">
-        <v>17</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I121" t="b">
-        <v>1</v>
-      </c>
-      <c r="J121" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>359</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="C122" t="s">
         <v>17</v>
@@ -5211,241 +5987,307 @@
       <c r="E122" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I122" t="b">
-        <v>1</v>
-      </c>
-      <c r="J122" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="F122" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H122" t="s">
+        <v>29</v>
+      </c>
+      <c r="I122" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K122" t="b">
+        <v>1</v>
+      </c>
+      <c r="L122" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C123" t="s">
         <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F123" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="I123" t="b">
-        <v>1</v>
-      </c>
-      <c r="J123" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+      <c r="I123" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J123" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K123" t="b">
+        <v>1</v>
+      </c>
+      <c r="L123" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C124" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="I124" t="b">
-        <v>0</v>
-      </c>
-      <c r="J124" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="I124" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J124" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K124" t="b">
+        <v>1</v>
+      </c>
+      <c r="L124" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
       </c>
       <c r="D125" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I125" t="b">
-        <v>1</v>
-      </c>
-      <c r="J125" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="F125" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="I125" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J125" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K125" t="b">
+        <v>1</v>
+      </c>
+      <c r="L125" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>364</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C126" t="s">
+        <v>26</v>
+      </c>
+      <c r="D126" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I126" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J126" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>367</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I127" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J127" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K127" t="b">
+        <v>1</v>
+      </c>
+      <c r="L127" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
         <v>369</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C126" t="s">
-        <v>26</v>
-      </c>
-      <c r="D126" t="s">
-        <v>26</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="C128" t="s">
+        <v>26</v>
+      </c>
+      <c r="D128" t="s">
+        <v>26</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F128" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I126" t="b">
-        <v>0</v>
-      </c>
-      <c r="J126" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+      <c r="I128" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J128" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
         <v>373</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C127" t="s">
-        <v>17</v>
-      </c>
-      <c r="D127" t="s">
-        <v>17</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F129" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="I127" t="b">
-        <v>0</v>
-      </c>
-      <c r="J127" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="323" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+      <c r="I129" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J129" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="323" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
         <v>377</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B130" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C128" t="s">
-        <v>26</v>
-      </c>
-      <c r="D128" t="s">
-        <v>26</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="C130" t="s">
+        <v>26</v>
+      </c>
+      <c r="D130" t="s">
+        <v>26</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F130" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="I128" t="b">
-        <v>0</v>
-      </c>
-      <c r="J128" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+      <c r="I130" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J130" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
         <v>381</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C131" t="s">
         <v>123</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D131" t="s">
         <v>123</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E131" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F131" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I129" t="b">
-        <v>0</v>
-      </c>
-      <c r="J129" t="s">
+      <c r="I131" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J131" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+      <c r="L131" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+    <row r="132" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
         <v>385</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="C130" t="s">
-        <v>17</v>
-      </c>
-      <c r="D130" t="s">
-        <v>17</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I130" t="b">
-        <v>1</v>
-      </c>
-      <c r="J130" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>387</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C131" t="s">
-        <v>17</v>
-      </c>
-      <c r="D131" t="s">
-        <v>12</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="I131" t="b">
-        <v>0</v>
-      </c>
-      <c r="J131" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>390</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -5456,235 +6298,295 @@
       <c r="E132" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I132" t="b">
-        <v>1</v>
-      </c>
-      <c r="J132" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I132" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J132" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K132" t="b">
+        <v>1</v>
+      </c>
+      <c r="L132" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
+        <v>387</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C133" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I133" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J133" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K133" t="b">
+        <v>0</v>
+      </c>
+      <c r="L133" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>390</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I134" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J134" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K134" t="b">
+        <v>1</v>
+      </c>
+      <c r="L134" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
         <v>392</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B135" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C135" t="s">
         <v>12</v>
       </c>
-      <c r="D133" t="s">
-        <v>26</v>
-      </c>
-      <c r="E133" s="1" t="s">
+      <c r="D135" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="I133" t="b">
-        <v>1</v>
-      </c>
-      <c r="J133" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+      <c r="I135" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K135" t="b">
+        <v>1</v>
+      </c>
+      <c r="L135" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
         <v>395</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C134" t="s">
-        <v>26</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="C136" t="s">
+        <v>26</v>
+      </c>
+      <c r="D136" t="s">
         <v>123</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E136" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="I134" t="b">
-        <v>0</v>
-      </c>
-      <c r="J134" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="102" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
+      <c r="I136" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
         <v>399</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B137" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C135" t="s">
-        <v>21</v>
-      </c>
-      <c r="D135" t="s">
-        <v>21</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="C137" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" t="s">
+        <v>21</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="I135" t="b">
-        <v>0</v>
-      </c>
-      <c r="J135" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
+      <c r="I137" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K137" t="b">
+        <v>0</v>
+      </c>
+      <c r="L137" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
         <v>402</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B138" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C136" t="s">
-        <v>17</v>
-      </c>
-      <c r="D136" t="s">
-        <v>17</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I136" t="b">
-        <v>1</v>
-      </c>
-      <c r="J136" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
+      <c r="I138" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J138" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K138" t="b">
+        <v>1</v>
+      </c>
+      <c r="L138" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
         <v>404</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C137" t="s">
-        <v>17</v>
-      </c>
-      <c r="D137" t="s">
-        <v>17</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I137" t="b">
-        <v>1</v>
-      </c>
-      <c r="J137" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="221" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
+      <c r="I139" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J139" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K139" t="b">
+        <v>1</v>
+      </c>
+      <c r="L139" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>406</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C138" t="s">
-        <v>21</v>
-      </c>
-      <c r="D138" t="s">
-        <v>21</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="C140" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" t="s">
+        <v>21</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="H138" t="s">
+      <c r="H140" t="s">
         <v>29</v>
       </c>
-      <c r="I138" t="b">
-        <v>0</v>
-      </c>
-      <c r="J138" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
+      <c r="I140" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J140" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
         <v>410</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C139" t="s">
-        <v>26</v>
-      </c>
-      <c r="D139" t="s">
-        <v>26</v>
-      </c>
-      <c r="E139" s="1" t="s">
+      <c r="C141" t="s">
+        <v>26</v>
+      </c>
+      <c r="D141" t="s">
+        <v>26</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="I139" t="b">
-        <v>0</v>
-      </c>
-      <c r="J139" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+      <c r="I141" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J141" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
         <v>413</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="C140" t="s">
-        <v>17</v>
-      </c>
-      <c r="D140" t="s">
-        <v>17</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I140" t="b">
-        <v>1</v>
-      </c>
-      <c r="J140" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>415</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C141" t="s">
-        <v>17</v>
-      </c>
-      <c r="D141" t="s">
-        <v>17</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I141" t="b">
-        <v>1</v>
-      </c>
-      <c r="J141" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>417</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -5695,155 +6597,185 @@
       <c r="E142" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I142" t="b">
-        <v>1</v>
-      </c>
-      <c r="J142" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I142" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J142" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K142" t="b">
+        <v>1</v>
+      </c>
+      <c r="L142" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>415</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I143" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J143" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K143" t="b">
+        <v>1</v>
+      </c>
+      <c r="L143" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>417</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J144" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K144" t="b">
+        <v>1</v>
+      </c>
+      <c r="L144" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
         <v>419</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B145" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C145" t="s">
         <v>123</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D145" t="s">
         <v>123</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="G143" t="s">
+      <c r="G145" t="s">
         <v>29</v>
       </c>
-      <c r="I143" t="b">
-        <v>0</v>
-      </c>
-      <c r="J143" t="s">
+      <c r="I145" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J145" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="144" spans="1:10" s="8" customFormat="1" ht="170" x14ac:dyDescent="0.2">
-      <c r="A144" s="8" t="s">
+    <row r="146" spans="1:12" s="8" customFormat="1" ht="170" x14ac:dyDescent="0.2">
+      <c r="A146" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B146" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C146" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D144" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E144" s="9" t="s">
+      <c r="D146" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E146" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="F144" s="9" t="s">
+      <c r="F146" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="G144" s="8" t="s">
+      <c r="G146" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H144" s="8" t="s">
+      <c r="H146" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I144" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J144" s="8" t="s">
+      <c r="I146" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J146" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K146" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L146" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
+    <row r="147" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
         <v>427</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C145" t="s">
-        <v>26</v>
-      </c>
-      <c r="D145" t="s">
-        <v>26</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="C147" t="s">
+        <v>26</v>
+      </c>
+      <c r="D147" t="s">
+        <v>26</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="I145" t="b">
-        <v>0</v>
-      </c>
-      <c r="J145" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
+      <c r="I147" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J147" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K147" t="b">
+        <v>0</v>
+      </c>
+      <c r="L147" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
         <v>430</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>17</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I146" t="b">
-        <v>1</v>
-      </c>
-      <c r="J146" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="136" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>432</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C147" t="s">
-        <v>21</v>
-      </c>
-      <c r="D147" t="s">
-        <v>21</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="H147" t="s">
-        <v>29</v>
-      </c>
-      <c r="I147" t="b">
-        <v>0</v>
-      </c>
-      <c r="J147" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>435</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -5854,65 +6786,89 @@
       <c r="E148" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I148" t="b">
-        <v>1</v>
-      </c>
-      <c r="J148" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I148" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J148" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K148" t="b">
+        <v>1</v>
+      </c>
+      <c r="L148" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
+        <v>432</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C149" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" t="s">
+        <v>21</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H149" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J149" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
+      <c r="L149" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>435</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I150" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J150" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K150" t="b">
+        <v>1</v>
+      </c>
+      <c r="L150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
         <v>437</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B151" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" t="s">
-        <v>17</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I149" t="b">
-        <v>1</v>
-      </c>
-      <c r="J149" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="388" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>439</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="C150" t="s">
-        <v>21</v>
-      </c>
-      <c r="D150" t="s">
-        <v>21</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="I150" t="b">
-        <v>0</v>
-      </c>
-      <c r="J150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>442</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -5923,42 +6879,54 @@
       <c r="E151" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I151" t="b">
-        <v>0</v>
-      </c>
-      <c r="J151" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I151" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J151" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K151" t="b">
+        <v>1</v>
+      </c>
+      <c r="L151" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="388" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C152" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D152" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="I152" t="b">
-        <v>0</v>
-      </c>
-      <c r="J152" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>441</v>
+      </c>
+      <c r="I152" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K152" t="b">
+        <v>0</v>
+      </c>
+      <c r="L152" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
@@ -5969,183 +6937,231 @@
       <c r="E153" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I153" t="b">
-        <v>1</v>
-      </c>
-      <c r="J153" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="I153" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J153" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
+      </c>
+      <c r="L153" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
+        <v>444</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="I154" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J154" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
+      </c>
+      <c r="L154" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>447</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I155" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J155" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K155" t="b">
+        <v>1</v>
+      </c>
+      <c r="L155" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
         <v>449</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C154" t="s">
-        <v>21</v>
-      </c>
-      <c r="D154" t="s">
-        <v>21</v>
-      </c>
-      <c r="E154" s="1" t="s">
+      <c r="C156" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" t="s">
+        <v>21</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="I154" t="b">
-        <v>0</v>
-      </c>
-      <c r="J154" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
+      <c r="I156" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J156" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
+      </c>
+      <c r="L156" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>451</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>17</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I155" t="b">
-        <v>1</v>
-      </c>
-      <c r="J155" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="136" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
+      <c r="I157" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J157" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K157" t="b">
+        <v>1</v>
+      </c>
+      <c r="L157" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
         <v>454</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C156" t="s">
-        <v>21</v>
-      </c>
-      <c r="D156" t="s">
-        <v>21</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="C158" t="s">
+        <v>21</v>
+      </c>
+      <c r="D158" t="s">
+        <v>21</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="I156" t="b">
-        <v>0</v>
-      </c>
-      <c r="J156" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="136" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
+      <c r="I158" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J158" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>457</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B159" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C157" t="s">
-        <v>21</v>
-      </c>
-      <c r="D157" t="s">
-        <v>21</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="C159" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" t="s">
+        <v>21</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="I157" t="b">
-        <v>0</v>
-      </c>
-      <c r="J157" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
+      <c r="I159" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J159" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
         <v>460</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B160" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C160" t="s">
         <v>12</v>
       </c>
-      <c r="D158" t="s">
-        <v>26</v>
-      </c>
-      <c r="E158" s="1" t="s">
+      <c r="D160" t="s">
+        <v>26</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="F158" s="1" t="s">
+      <c r="F160" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="I158" t="b">
-        <v>1</v>
-      </c>
-      <c r="J158" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="187" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
+      <c r="I160" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J160" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K160" t="b">
+        <v>1</v>
+      </c>
+      <c r="L160" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
         <v>464</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C159" t="s">
-        <v>17</v>
-      </c>
-      <c r="D159" t="s">
-        <v>17</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I159" t="b">
-        <v>1</v>
-      </c>
-      <c r="J159" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>466</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C160" t="s">
-        <v>17</v>
-      </c>
-      <c r="D160" t="s">
-        <v>17</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I160" t="b">
-        <v>1</v>
-      </c>
-      <c r="J160" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>468</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
@@ -6156,229 +7172,289 @@
       <c r="E161" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I161" t="b">
-        <v>1</v>
-      </c>
-      <c r="J161" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="I161" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J161" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K161" t="b">
+        <v>1</v>
+      </c>
+      <c r="L161" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>466</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I162" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J162" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K162" t="b">
+        <v>1</v>
+      </c>
+      <c r="L162" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>468</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I163" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J163" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K163" t="b">
+        <v>1</v>
+      </c>
+      <c r="L163" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>470</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B164" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C162" t="s">
-        <v>21</v>
-      </c>
-      <c r="D162" t="s">
-        <v>21</v>
-      </c>
-      <c r="E162" s="1" t="s">
+      <c r="C164" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" t="s">
+        <v>21</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I162" t="b">
-        <v>0</v>
-      </c>
-      <c r="J162" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="204" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
+      <c r="I164" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J164" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
         <v>473</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B165" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C163" t="s">
-        <v>26</v>
-      </c>
-      <c r="D163" t="s">
-        <v>26</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="C165" t="s">
+        <v>26</v>
+      </c>
+      <c r="D165" t="s">
+        <v>26</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="I163" t="b">
-        <v>0</v>
-      </c>
-      <c r="J163" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="102" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
+      <c r="I165" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J165" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
         <v>476</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C164" t="s">
-        <v>17</v>
-      </c>
-      <c r="D164" t="s">
-        <v>17</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I164" t="b">
-        <v>1</v>
-      </c>
-      <c r="J164" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
+      <c r="I166" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J166" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K166" t="b">
+        <v>1</v>
+      </c>
+      <c r="L166" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
         <v>478</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C165" t="s">
-        <v>17</v>
-      </c>
-      <c r="D165" t="s">
-        <v>17</v>
-      </c>
-      <c r="E165" s="1" t="s">
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I165" t="b">
-        <v>1</v>
-      </c>
-      <c r="J165" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
+      <c r="I167" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J167" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K167" t="b">
+        <v>1</v>
+      </c>
+      <c r="L167" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
         <v>480</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C168" t="s">
         <v>12</v>
       </c>
-      <c r="D166" t="s">
-        <v>26</v>
-      </c>
-      <c r="E166" s="1" t="s">
+      <c r="D168" t="s">
+        <v>26</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="F166" s="1" t="s">
+      <c r="F168" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="I166" t="b">
-        <v>1</v>
-      </c>
-      <c r="J166" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="272" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
+      <c r="I168" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J168" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K168" t="b">
+        <v>1</v>
+      </c>
+      <c r="L168" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
         <v>483</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B169" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C167" t="s">
-        <v>26</v>
-      </c>
-      <c r="D167" t="s">
-        <v>26</v>
-      </c>
-      <c r="E167" s="1" t="s">
+      <c r="C169" t="s">
+        <v>26</v>
+      </c>
+      <c r="D169" t="s">
+        <v>26</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="I167" t="b">
-        <v>0</v>
-      </c>
-      <c r="J167" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
+      <c r="I169" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J169" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
         <v>486</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C168" t="s">
-        <v>17</v>
-      </c>
-      <c r="D168" t="s">
-        <v>17</v>
-      </c>
-      <c r="E168" s="1" t="s">
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I168" t="b">
-        <v>1</v>
-      </c>
-      <c r="J168" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
+      <c r="I170" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J170" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K170" t="b">
+        <v>1</v>
+      </c>
+      <c r="L170" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
         <v>488</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="C169" t="s">
-        <v>17</v>
-      </c>
-      <c r="D169" t="s">
-        <v>17</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I169" t="b">
-        <v>1</v>
-      </c>
-      <c r="J169" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>490</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C170" t="s">
-        <v>26</v>
-      </c>
-      <c r="D170" t="s">
-        <v>26</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="I170" t="b">
-        <v>0</v>
-      </c>
-      <c r="J170" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>493</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -6389,45 +7465,54 @@
       <c r="E171" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I171" t="b">
-        <v>1</v>
-      </c>
-      <c r="J171" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="187" x14ac:dyDescent="0.2">
+      <c r="I171" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J171" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K171" t="b">
+        <v>1</v>
+      </c>
+      <c r="L171" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C172" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="D172" t="s">
         <v>26</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G172" t="s">
-        <v>29</v>
-      </c>
-      <c r="I172" t="b">
-        <v>0</v>
-      </c>
-      <c r="J172" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+      <c r="I172" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J172" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
@@ -6438,42 +7523,57 @@
       <c r="E173" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I173" t="b">
-        <v>1</v>
-      </c>
-      <c r="J173" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="I173" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J173" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K173" t="b">
+        <v>1</v>
+      </c>
+      <c r="L173" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C174" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="D174" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I174" t="b">
-        <v>1</v>
-      </c>
-      <c r="J174" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+      <c r="G174" t="s">
+        <v>29</v>
+      </c>
+      <c r="I174" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J174" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+      <c r="L174" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
@@ -6484,264 +7584,330 @@
       <c r="E175" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I175" t="b">
-        <v>1</v>
-      </c>
-      <c r="J175" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="I175" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J175" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K175" t="b">
+        <v>1</v>
+      </c>
+      <c r="L175" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>500</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>17</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I176" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J176" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K176" t="b">
+        <v>1</v>
+      </c>
+      <c r="L176" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>502</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>17</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I177" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J177" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K177" t="b">
+        <v>1</v>
+      </c>
+      <c r="L177" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
         <v>504</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B178" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="C176" t="s">
-        <v>17</v>
-      </c>
-      <c r="D176" t="s">
-        <v>17</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>17</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F176" s="1" t="s">
+      <c r="F178" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="I176" t="b">
-        <v>0</v>
-      </c>
-      <c r="J176" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
+      <c r="I178" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J178" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
         <v>508</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B179" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C177" t="s">
-        <v>26</v>
-      </c>
-      <c r="D177" t="s">
+      <c r="C179" t="s">
+        <v>26</v>
+      </c>
+      <c r="D179" t="s">
         <v>123</v>
       </c>
-      <c r="E177" s="1" t="s">
+      <c r="E179" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="I177" t="b">
-        <v>0</v>
-      </c>
-      <c r="J177" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
+      <c r="I179" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J179" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K179" t="b">
+        <v>0</v>
+      </c>
+      <c r="L179" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
         <v>511</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B180" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C178" t="s">
-        <v>17</v>
-      </c>
-      <c r="D178" t="s">
-        <v>17</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>17</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F178" s="1" t="s">
+      <c r="F180" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="H178" t="s">
+      <c r="H180" t="s">
         <v>29</v>
       </c>
-      <c r="I178" t="b">
-        <v>1</v>
-      </c>
-      <c r="J178" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="372" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
+      <c r="I180" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J180" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K180" t="b">
+        <v>1</v>
+      </c>
+      <c r="L180" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
         <v>514</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B181" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C181" t="s">
         <v>68</v>
       </c>
-      <c r="D179" t="s">
-        <v>21</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="D181" t="s">
+        <v>21</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F179" s="1" t="s">
+      <c r="F181" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="H179" t="s">
+      <c r="H181" t="s">
         <v>29</v>
       </c>
-      <c r="I179" t="b">
-        <v>0</v>
-      </c>
-      <c r="J179" t="s">
+      <c r="I181" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J181" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+      <c r="L181" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="204" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
+    <row r="182" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
         <v>518</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C180" t="s">
-        <v>26</v>
-      </c>
-      <c r="D180" t="s">
-        <v>26</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="C182" t="s">
+        <v>26</v>
+      </c>
+      <c r="D182" t="s">
+        <v>26</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="I180" t="b">
-        <v>0</v>
-      </c>
-      <c r="J180" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
+      <c r="I182" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J182" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
         <v>521</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B183" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="C181" t="s">
-        <v>17</v>
-      </c>
-      <c r="D181" t="s">
-        <v>17</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I181" t="b">
-        <v>1</v>
-      </c>
-      <c r="J181" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="272" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
+      <c r="I183" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J183" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K183" t="b">
+        <v>1</v>
+      </c>
+      <c r="L183" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
         <v>523</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C182" t="s">
-        <v>26</v>
-      </c>
-      <c r="D182" t="s">
-        <v>26</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="C184" t="s">
+        <v>26</v>
+      </c>
+      <c r="D184" t="s">
+        <v>26</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="I182" t="b">
-        <v>0</v>
-      </c>
-      <c r="J182" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
+      <c r="I184" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J184" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
         <v>526</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B185" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C185" t="s">
         <v>12</v>
       </c>
-      <c r="D183" t="s">
-        <v>26</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="D185" t="s">
+        <v>26</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I183" t="b">
-        <v>1</v>
-      </c>
-      <c r="J183" t="s">
+      <c r="I185" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J185" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K185" t="b">
+        <v>1</v>
+      </c>
+      <c r="L185" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
+    <row r="186" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
         <v>528</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B186" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="C184" t="s">
-        <v>17</v>
-      </c>
-      <c r="D184" t="s">
-        <v>17</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I184" t="b">
-        <v>1</v>
-      </c>
-      <c r="J184" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="204" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>530</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C185" t="s">
-        <v>21</v>
-      </c>
-      <c r="D185" t="s">
-        <v>21</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="I185" t="b">
-        <v>0</v>
-      </c>
-      <c r="J185" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
-        <v>532</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="C186" t="s">
         <v>17</v>
@@ -6752,345 +7918,487 @@
       <c r="E186" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I186" t="b">
-        <v>1</v>
-      </c>
-      <c r="J186" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="I186" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J186" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K186" t="b">
+        <v>1</v>
+      </c>
+      <c r="L186" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>530</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C187" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" t="s">
+        <v>21</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I187" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J187" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>532</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>17</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I188" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J188" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K188" t="b">
+        <v>1</v>
+      </c>
+      <c r="L188" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
         <v>534</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B189" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C189" t="s">
         <v>123</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D189" t="s">
         <v>123</v>
       </c>
-      <c r="E187" s="1" t="s">
+      <c r="E189" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="F189" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="H187" t="s">
+      <c r="H189" t="s">
         <v>29</v>
       </c>
-      <c r="I187" t="b">
-        <v>0</v>
-      </c>
-      <c r="J187" t="s">
+      <c r="I189" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J189" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="272" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
+    <row r="190" spans="1:12" ht="272" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
         <v>538</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="B190" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="C188" t="s">
-        <v>17</v>
-      </c>
-      <c r="D188" t="s">
-        <v>26</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>26</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="F190" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="H188" t="s">
+      <c r="H190" t="s">
         <v>29</v>
       </c>
-      <c r="I188" t="b">
-        <v>0</v>
-      </c>
-      <c r="J188" t="s">
+      <c r="I190" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J190" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
+    <row r="191" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
         <v>542</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B191" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C189" t="s">
-        <v>17</v>
-      </c>
-      <c r="D189" t="s">
-        <v>17</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I189" t="b">
-        <v>1</v>
-      </c>
-      <c r="J189" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
+      <c r="I191" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J191" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K191" t="b">
+        <v>1</v>
+      </c>
+      <c r="L191" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
         <v>544</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B192" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C190" t="s">
-        <v>17</v>
-      </c>
-      <c r="D190" t="s">
-        <v>17</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>17</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I190" t="b">
-        <v>1</v>
-      </c>
-      <c r="J190" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
+      <c r="I192" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J192" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K192" t="b">
+        <v>1</v>
+      </c>
+      <c r="L192" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
         <v>546</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B193" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C193" t="s">
         <v>12</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D193" t="s">
         <v>12</v>
       </c>
-      <c r="E191" s="1" t="s">
+      <c r="E193" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F191" s="1" t="s">
+      <c r="F193" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="I191" t="b">
-        <v>1</v>
-      </c>
-      <c r="J191" t="s">
+      <c r="I193" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J193" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K193" t="b">
+        <v>1</v>
+      </c>
+      <c r="L193" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="238" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
+    <row r="194" spans="1:12" ht="238" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
         <v>550</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B194" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C192" t="s">
-        <v>26</v>
-      </c>
-      <c r="D192" t="s">
-        <v>26</v>
-      </c>
-      <c r="E192" s="1" t="s">
+      <c r="C194" t="s">
+        <v>26</v>
+      </c>
+      <c r="D194" t="s">
+        <v>26</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F192" s="1" t="s">
+      <c r="F194" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="I192" t="b">
-        <v>0</v>
-      </c>
-      <c r="J192" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A193" t="s">
+      <c r="I194" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J194" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K194" t="b">
+        <v>0</v>
+      </c>
+      <c r="L194" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
         <v>554</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="B195" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C195" t="s">
         <v>123</v>
       </c>
-      <c r="D193" t="s">
-        <v>26</v>
-      </c>
-      <c r="E193" s="1" t="s">
+      <c r="D195" t="s">
+        <v>26</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="F193" s="1" t="s">
+      <c r="F195" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="I193" t="b">
-        <v>0</v>
-      </c>
-      <c r="J193" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A194" t="s">
+      <c r="I195" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J195" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K195" t="b">
+        <v>0</v>
+      </c>
+      <c r="L195" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
         <v>558</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B196" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C194" t="s">
-        <v>17</v>
-      </c>
-      <c r="D194" t="s">
-        <v>17</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="C196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I194" t="b">
-        <v>1</v>
-      </c>
-      <c r="J194" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A195" t="s">
+      <c r="I196" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J196" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K196" t="b">
+        <v>1</v>
+      </c>
+      <c r="L196" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
         <v>560</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="C195" t="s">
-        <v>26</v>
-      </c>
-      <c r="D195" t="s">
-        <v>26</v>
-      </c>
-      <c r="E195" s="1" t="s">
+      <c r="C197" t="s">
+        <v>26</v>
+      </c>
+      <c r="D197" t="s">
+        <v>26</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F195" s="1" t="s">
+      <c r="F197" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="I195" t="b">
-        <v>0</v>
-      </c>
-      <c r="J195" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A196" t="s">
+      <c r="I197" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J197" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K197" t="b">
+        <v>0</v>
+      </c>
+      <c r="L197" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
         <v>564</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B198" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C198" t="s">
         <v>68</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D198" t="s">
         <v>68</v>
       </c>
-      <c r="E196" s="1" t="s">
+      <c r="E198" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="I196" t="b">
-        <v>0</v>
-      </c>
-      <c r="J196" t="s">
+      <c r="I198" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J198" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K198" t="b">
+        <v>0</v>
+      </c>
+      <c r="L198" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="404" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
+    <row r="199" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
         <v>567</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="B199" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="C197" t="s">
-        <v>123</v>
-      </c>
-      <c r="D197" t="s">
-        <v>26</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="H197" t="s">
-        <v>29</v>
-      </c>
-      <c r="I197" t="b">
-        <v>0</v>
-      </c>
-      <c r="J197" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
-        <v>571</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="C198" t="s">
-        <v>17</v>
-      </c>
-      <c r="D198" t="s">
-        <v>17</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I198" t="b">
-        <v>1</v>
-      </c>
-      <c r="J198" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="356" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
-        <v>573</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>574</v>
       </c>
       <c r="C199" t="s">
         <v>123</v>
       </c>
       <c r="D199" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="H199" t="s">
         <v>29</v>
       </c>
-      <c r="I199" t="b">
-        <v>0</v>
-      </c>
-      <c r="J199" t="s">
+      <c r="I199" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J199" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K199" t="b">
+        <v>0</v>
+      </c>
+      <c r="L199" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>571</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I200" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="J200" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K200" t="b">
+        <v>1</v>
+      </c>
+      <c r="L200" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" ht="356" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>573</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C201" t="s">
+        <v>123</v>
+      </c>
+      <c r="D201" t="s">
+        <v>123</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="H201" t="s">
+        <v>29</v>
+      </c>
+      <c r="I201" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J201" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K201" t="b">
+        <v>0</v>
+      </c>
+      <c r="L201" t="s">
         <v>123</v>
       </c>
     </row>
